--- a/data/aim2.1platecounts_clean.xlsx
+++ b/data/aim2.1platecounts_clean.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G325"/>
+  <dimension ref="A1:G271"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2067,11 +2067,11 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2093,16 +2093,16 @@
         </is>
       </c>
       <c r="G56">
-        <v>24500000</v>
+        <v>2012500000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2129,11 +2129,11 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="G58">
-        <v>2041666.666666667</v>
+        <v>167708333.3333333</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2186,16 +2186,16 @@
         </is>
       </c>
       <c r="G59">
-        <v>40750000</v>
+        <v>11250000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2222,11 +2222,11 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         </is>
       </c>
       <c r="G61">
-        <v>3395833.333333333</v>
+        <v>937500000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2279,16 +2279,16 @@
         </is>
       </c>
       <c r="G62">
-        <v>36416666.66666667</v>
+        <v>4125000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2315,11 +2315,11 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2341,16 +2341,16 @@
         </is>
       </c>
       <c r="G64">
-        <v>3034722.222222222</v>
+        <v>343750000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2372,16 +2372,16 @@
         </is>
       </c>
       <c r="G65">
-        <v>2012500000</v>
+        <v>358750000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2408,11 +2408,11 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2434,16 +2434,16 @@
         </is>
       </c>
       <c r="G67">
-        <v>167708333.3333333</v>
+        <v>29895833.33333333</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2465,16 +2465,16 @@
         </is>
       </c>
       <c r="G68">
-        <v>11250000000</v>
+        <v>277500000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2501,11 +2501,11 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="G70">
-        <v>937500000</v>
+        <v>23125000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2558,16 +2558,16 @@
         </is>
       </c>
       <c r="G71">
-        <v>4125000000</v>
+        <v>737500000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2594,11 +2594,11 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2620,16 +2620,16 @@
         </is>
       </c>
       <c r="G73">
-        <v>343750000</v>
+        <v>61458333.33333334</v>
       </c>
     </row>
     <row r="74">
       <c r="A74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2651,16 +2651,16 @@
         </is>
       </c>
       <c r="G74">
-        <v>358750000</v>
+        <v>4500000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2687,11 +2687,11 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2713,16 +2713,16 @@
         </is>
       </c>
       <c r="G76">
-        <v>29895833.33333333</v>
+        <v>375000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2744,16 +2744,16 @@
         </is>
       </c>
       <c r="G77">
-        <v>277500000</v>
+        <v>6500000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2780,11 +2780,11 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2806,16 +2806,16 @@
         </is>
       </c>
       <c r="G79">
-        <v>23125000</v>
+        <v>541666666.6666666</v>
       </c>
     </row>
     <row r="80">
       <c r="A80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2837,16 +2837,16 @@
         </is>
       </c>
       <c r="G80">
-        <v>737500000</v>
+        <v>5750000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2873,11 +2873,11 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2899,16 +2899,16 @@
         </is>
       </c>
       <c r="G82">
-        <v>61458333.33333334</v>
+        <v>479166666.6666667</v>
       </c>
     </row>
     <row r="83">
       <c r="A83">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2930,16 +2930,16 @@
         </is>
       </c>
       <c r="G83">
-        <v>4500000000</v>
+        <v>3787500000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2966,11 +2966,11 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2992,16 +2992,16 @@
         </is>
       </c>
       <c r="G85">
-        <v>375000000</v>
+        <v>315625000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3023,16 +3023,16 @@
         </is>
       </c>
       <c r="G86">
-        <v>6500000000</v>
+        <v>4750000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3059,11 +3059,11 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="G88">
-        <v>541666666.6666666</v>
+        <v>395833333.3333333</v>
       </c>
     </row>
     <row r="89">
       <c r="A89">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3116,16 +3116,16 @@
         </is>
       </c>
       <c r="G89">
-        <v>5750000000</v>
+        <v>5250000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3152,11 +3152,11 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3178,16 +3178,16 @@
         </is>
       </c>
       <c r="G91">
-        <v>479166666.6666667</v>
+        <v>437500000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="D92">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3209,16 +3209,16 @@
         </is>
       </c>
       <c r="G92">
-        <v>3787500000</v>
+        <v>1962500000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3227,7 +3227,7 @@
         </is>
       </c>
       <c r="D93">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3245,11 +3245,11 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="D94">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3271,16 +3271,16 @@
         </is>
       </c>
       <c r="G94">
-        <v>315625000</v>
+        <v>163541666.6666667</v>
       </c>
     </row>
     <row r="95">
       <c r="A95">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="D95">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3302,16 +3302,16 @@
         </is>
       </c>
       <c r="G95">
-        <v>4750000000</v>
+        <v>575000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3320,7 +3320,7 @@
         </is>
       </c>
       <c r="D96">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3338,11 +3338,11 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="D97">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3364,16 +3364,16 @@
         </is>
       </c>
       <c r="G97">
-        <v>395833333.3333333</v>
+        <v>47916666.66666666</v>
       </c>
     </row>
     <row r="98">
       <c r="A98">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="D98">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3395,16 +3395,16 @@
         </is>
       </c>
       <c r="G98">
-        <v>5250000000</v>
+        <v>1250000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="D99">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3431,11 +3431,11 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3444,7 +3444,7 @@
         </is>
       </c>
       <c r="D100">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3457,16 +3457,16 @@
         </is>
       </c>
       <c r="G100">
-        <v>437500000</v>
+        <v>104166666.6666667</v>
       </c>
     </row>
     <row r="101">
       <c r="A101">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3488,16 +3488,16 @@
         </is>
       </c>
       <c r="G101">
-        <v>1962500000</v>
+        <v>4625000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3524,11 +3524,11 @@
     </row>
     <row r="103">
       <c r="A103">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3550,16 +3550,16 @@
         </is>
       </c>
       <c r="G103">
-        <v>163541666.6666667</v>
+        <v>385416666.6666667</v>
       </c>
     </row>
     <row r="104">
       <c r="A104">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3581,16 +3581,16 @@
         </is>
       </c>
       <c r="G104">
-        <v>575000000</v>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3617,11 +3617,11 @@
     </row>
     <row r="106">
       <c r="A106">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3643,16 +3643,16 @@
         </is>
       </c>
       <c r="G106">
-        <v>47916666.66666666</v>
+        <v>833333333.3333334</v>
       </c>
     </row>
     <row r="107">
       <c r="A107">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3674,16 +3674,16 @@
         </is>
       </c>
       <c r="G107">
-        <v>1250000000</v>
+        <v>1650000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3710,11 +3710,11 @@
     </row>
     <row r="109">
       <c r="A109">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3736,16 +3736,16 @@
         </is>
       </c>
       <c r="G109">
-        <v>104166666.6666667</v>
+        <v>137500000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3767,16 +3767,16 @@
         </is>
       </c>
       <c r="G110">
-        <v>4625000000</v>
+        <v>367500000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3803,11 +3803,11 @@
     </row>
     <row r="112">
       <c r="A112">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3829,16 +3829,16 @@
         </is>
       </c>
       <c r="G112">
-        <v>385416666.6666667</v>
+        <v>30625000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3860,16 +3860,16 @@
         </is>
       </c>
       <c r="G113">
-        <v>10000000000</v>
+        <v>366875000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3896,11 +3896,11 @@
     </row>
     <row r="115">
       <c r="A115">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3922,16 +3922,16 @@
         </is>
       </c>
       <c r="G115">
-        <v>833333333.3333334</v>
+        <v>30572916.66666667</v>
       </c>
     </row>
     <row r="116">
       <c r="A116">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3953,16 +3953,16 @@
         </is>
       </c>
       <c r="G116">
-        <v>1650000000</v>
+        <v>1206875000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3989,11 +3989,11 @@
     </row>
     <row r="118">
       <c r="A118">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4015,16 +4015,16 @@
         </is>
       </c>
       <c r="G118">
-        <v>137500000</v>
+        <v>100572916.6666667</v>
       </c>
     </row>
     <row r="119">
       <c r="A119">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4033,7 +4033,7 @@
         </is>
       </c>
       <c r="D119">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4046,16 +4046,16 @@
         </is>
       </c>
       <c r="G119">
-        <v>9250000</v>
+        <v>2612500000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="D120">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4082,11 +4082,11 @@
     </row>
     <row r="121">
       <c r="A121">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="D121">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4108,16 +4108,16 @@
         </is>
       </c>
       <c r="G121">
-        <v>770833.3333333334</v>
+        <v>217708333.3333333</v>
       </c>
     </row>
     <row r="122">
       <c r="A122">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="D122">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4139,16 +4139,16 @@
         </is>
       </c>
       <c r="G122">
-        <v>16000000</v>
+        <v>3075000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="D123">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4175,11 +4175,11 @@
     </row>
     <row r="124">
       <c r="A124">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="D124">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4201,16 +4201,16 @@
         </is>
       </c>
       <c r="G124">
-        <v>1333333.333333333</v>
+        <v>256250000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="D125">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4232,16 +4232,16 @@
         </is>
       </c>
       <c r="G125">
-        <v>6750000</v>
+        <v>1537500000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="D126">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4268,11 +4268,11 @@
     </row>
     <row r="127">
       <c r="A127">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="D127">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4294,16 +4294,16 @@
         </is>
       </c>
       <c r="G127">
-        <v>562500</v>
+        <v>128125000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4325,16 +4325,16 @@
         </is>
       </c>
       <c r="G128">
-        <v>367500000</v>
+        <v>2300000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4361,11 +4361,11 @@
     </row>
     <row r="130">
       <c r="A130">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4387,16 +4387,16 @@
         </is>
       </c>
       <c r="G130">
-        <v>30625000</v>
+        <v>191666666.6666667</v>
       </c>
     </row>
     <row r="131">
       <c r="A131">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4418,16 +4418,16 @@
         </is>
       </c>
       <c r="G131">
-        <v>366875000</v>
+        <v>762500000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4454,11 +4454,11 @@
     </row>
     <row r="133">
       <c r="A133">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4480,16 +4480,16 @@
         </is>
       </c>
       <c r="G133">
-        <v>30572916.66666667</v>
+        <v>63541666.66666666</v>
       </c>
     </row>
     <row r="134">
       <c r="A134">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4511,16 +4511,16 @@
         </is>
       </c>
       <c r="G134">
-        <v>1206875000</v>
+        <v>650000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4547,11 +4547,11 @@
     </row>
     <row r="136">
       <c r="A136">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4573,16 +4573,16 @@
         </is>
       </c>
       <c r="G136">
-        <v>100572916.6666667</v>
+        <v>54166666.66666666</v>
       </c>
     </row>
     <row r="137">
       <c r="A137">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4591,11 +4591,11 @@
         </is>
       </c>
       <c r="D137">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -4604,16 +4604,16 @@
         </is>
       </c>
       <c r="G137">
-        <v>2612500000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4622,11 +4622,11 @@
         </is>
       </c>
       <c r="D138">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -4635,16 +4635,16 @@
         </is>
       </c>
       <c r="G138">
-        <v>0</v>
+        <v>40500000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4653,11 +4653,11 @@
         </is>
       </c>
       <c r="D139">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -4666,16 +4666,16 @@
         </is>
       </c>
       <c r="G139">
-        <v>217708333.3333333</v>
+        <v>3375000.083333333</v>
       </c>
     </row>
     <row r="140">
       <c r="A140">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4684,11 +4684,11 @@
         </is>
       </c>
       <c r="D140">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -4697,16 +4697,16 @@
         </is>
       </c>
       <c r="G140">
-        <v>3075000000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4715,11 +4715,11 @@
         </is>
       </c>
       <c r="D141">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -4728,16 +4728,16 @@
         </is>
       </c>
       <c r="G141">
-        <v>0</v>
+        <v>40350000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4746,11 +4746,11 @@
         </is>
       </c>
       <c r="D142">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -4759,16 +4759,16 @@
         </is>
       </c>
       <c r="G142">
-        <v>256250000</v>
+        <v>3362500.083333333</v>
       </c>
     </row>
     <row r="143">
       <c r="A143">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4777,11 +4777,11 @@
         </is>
       </c>
       <c r="D143">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -4790,16 +4790,16 @@
         </is>
       </c>
       <c r="G143">
-        <v>1537500000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
       <c r="A144">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4808,11 +4808,11 @@
         </is>
       </c>
       <c r="D144">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -4821,16 +4821,16 @@
         </is>
       </c>
       <c r="G144">
-        <v>0</v>
+        <v>41299999.99999999</v>
       </c>
     </row>
     <row r="145">
       <c r="A145">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4839,11 +4839,11 @@
         </is>
       </c>
       <c r="D145">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -4852,16 +4852,16 @@
         </is>
       </c>
       <c r="G145">
-        <v>128125000</v>
+        <v>3441666.75</v>
       </c>
     </row>
     <row r="146">
       <c r="A146">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4870,11 +4870,11 @@
         </is>
       </c>
       <c r="D146">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -4883,16 +4883,16 @@
         </is>
       </c>
       <c r="G146">
-        <v>2300000000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4901,11 +4901,11 @@
         </is>
       </c>
       <c r="D147">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -4914,16 +4914,16 @@
         </is>
       </c>
       <c r="G147">
-        <v>0</v>
+        <v>277500000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4932,11 +4932,11 @@
         </is>
       </c>
       <c r="D148">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -4945,16 +4945,16 @@
         </is>
       </c>
       <c r="G148">
-        <v>191666666.6666667</v>
+        <v>23125000.08333333</v>
       </c>
     </row>
     <row r="149">
       <c r="A149">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4963,11 +4963,11 @@
         </is>
       </c>
       <c r="D149">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -4976,16 +4976,16 @@
         </is>
       </c>
       <c r="G149">
-        <v>762500000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4994,11 +4994,11 @@
         </is>
       </c>
       <c r="D150">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5007,16 +5007,16 @@
         </is>
       </c>
       <c r="G150">
-        <v>0</v>
+        <v>60000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5025,11 +5025,11 @@
         </is>
       </c>
       <c r="D151">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5038,16 +5038,16 @@
         </is>
       </c>
       <c r="G151">
-        <v>63541666.66666666</v>
+        <v>5000000.083333333</v>
       </c>
     </row>
     <row r="152">
       <c r="A152">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5056,11 +5056,11 @@
         </is>
       </c>
       <c r="D152">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5069,16 +5069,16 @@
         </is>
       </c>
       <c r="G152">
-        <v>650000000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5087,11 +5087,11 @@
         </is>
       </c>
       <c r="D153">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="G153">
-        <v>0</v>
+        <v>85500000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5118,11 +5118,11 @@
         </is>
       </c>
       <c r="D154">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5131,16 +5131,16 @@
         </is>
       </c>
       <c r="G154">
-        <v>54166666.66666666</v>
+        <v>7125000.083333333</v>
       </c>
     </row>
     <row r="155">
       <c r="A155">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5149,11 +5149,11 @@
         </is>
       </c>
       <c r="D155">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5162,16 +5162,16 @@
         </is>
       </c>
       <c r="G155">
-        <v>17375000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5180,11 +5180,11 @@
         </is>
       </c>
       <c r="D156">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5193,16 +5193,16 @@
         </is>
       </c>
       <c r="G156">
-        <v>0</v>
+        <v>439999.9999999999</v>
       </c>
     </row>
     <row r="157">
       <c r="A157">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5211,11 +5211,11 @@
         </is>
       </c>
       <c r="D157">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5224,16 +5224,16 @@
         </is>
       </c>
       <c r="G157">
-        <v>1447916.666666667</v>
+        <v>36666.74999999999</v>
       </c>
     </row>
     <row r="158">
       <c r="A158">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5242,11 +5242,11 @@
         </is>
       </c>
       <c r="D158">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5255,16 +5255,16 @@
         </is>
       </c>
       <c r="G158">
-        <v>13000000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
       <c r="A159">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5273,11 +5273,11 @@
         </is>
       </c>
       <c r="D159">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5286,16 +5286,16 @@
         </is>
       </c>
       <c r="G159">
-        <v>0</v>
+        <v>5800000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5304,11 +5304,11 @@
         </is>
       </c>
       <c r="D160">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -5317,16 +5317,16 @@
         </is>
       </c>
       <c r="G160">
-        <v>1083333.333333333</v>
+        <v>483333.4166666667</v>
       </c>
     </row>
     <row r="161">
       <c r="A161">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5335,11 +5335,11 @@
         </is>
       </c>
       <c r="D161">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -5348,16 +5348,16 @@
         </is>
       </c>
       <c r="G161">
-        <v>3375000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
       <c r="A162">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5366,11 +5366,11 @@
         </is>
       </c>
       <c r="D162">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -5379,16 +5379,16 @@
         </is>
       </c>
       <c r="G162">
-        <v>0</v>
+        <v>12450000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5397,11 +5397,11 @@
         </is>
       </c>
       <c r="D163">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>encapsulated</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -5410,16 +5410,16 @@
         </is>
       </c>
       <c r="G163">
-        <v>281250</v>
+        <v>1037500.083333333</v>
       </c>
     </row>
     <row r="164">
       <c r="A164">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5446,11 +5446,11 @@
     </row>
     <row r="165">
       <c r="A165">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5472,16 +5472,16 @@
         </is>
       </c>
       <c r="G165">
-        <v>40500000</v>
+        <v>51000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5503,16 +5503,16 @@
         </is>
       </c>
       <c r="G166">
-        <v>3375000.083333333</v>
+        <v>4250000.083333333</v>
       </c>
     </row>
     <row r="167">
       <c r="A167">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5539,11 +5539,11 @@
     </row>
     <row r="168">
       <c r="A168">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5565,16 +5565,16 @@
         </is>
       </c>
       <c r="G168">
-        <v>40350000</v>
+        <v>56000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5596,16 +5596,16 @@
         </is>
       </c>
       <c r="G169">
-        <v>3362500.083333333</v>
+        <v>4666666.75</v>
       </c>
     </row>
     <row r="170">
       <c r="A170">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5627,16 +5627,16 @@
         </is>
       </c>
       <c r="G170">
-        <v>1</v>
+        <v>16250</v>
       </c>
     </row>
     <row r="171">
       <c r="A171">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="G171">
-        <v>41299999.99999999</v>
+        <v>87000000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5689,16 +5689,16 @@
         </is>
       </c>
       <c r="G172">
-        <v>3441666.75</v>
+        <v>7251354.166666667</v>
       </c>
     </row>
     <row r="173">
       <c r="A173">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5720,16 +5720,16 @@
         </is>
       </c>
       <c r="G173">
-        <v>1</v>
+        <v>25750</v>
       </c>
     </row>
     <row r="174">
       <c r="A174">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5751,16 +5751,16 @@
         </is>
       </c>
       <c r="G174">
-        <v>277500000</v>
+        <v>231000000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5782,16 +5782,16 @@
         </is>
       </c>
       <c r="G175">
-        <v>23125000.08333333</v>
+        <v>19252145.83333333</v>
       </c>
     </row>
     <row r="176">
       <c r="A176">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5813,16 +5813,16 @@
         </is>
       </c>
       <c r="G176">
-        <v>1</v>
+        <v>35375</v>
       </c>
     </row>
     <row r="177">
       <c r="A177">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5844,16 +5844,16 @@
         </is>
       </c>
       <c r="G177">
-        <v>60000000</v>
+        <v>160500000</v>
       </c>
     </row>
     <row r="178">
       <c r="A178">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5875,16 +5875,16 @@
         </is>
       </c>
       <c r="G178">
-        <v>5000000.083333333</v>
+        <v>13377947.91666667</v>
       </c>
     </row>
     <row r="179">
       <c r="A179">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5906,16 +5906,16 @@
         </is>
       </c>
       <c r="G179">
-        <v>1</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5937,16 +5937,16 @@
         </is>
       </c>
       <c r="G180">
-        <v>85500000</v>
+        <v>181500000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5968,16 +5968,16 @@
         </is>
       </c>
       <c r="G181">
-        <v>7125000.083333333</v>
+        <v>15126833.33333333</v>
       </c>
     </row>
     <row r="182">
       <c r="A182">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5986,7 +5986,7 @@
         </is>
       </c>
       <c r="D182">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -5999,16 +5999,16 @@
         </is>
       </c>
       <c r="G182">
-        <v>1</v>
+        <v>2912500000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="D183">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -6030,16 +6030,16 @@
         </is>
       </c>
       <c r="G183">
-        <v>439999.9999999999</v>
+        <v>195500000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="D184">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -6061,16 +6061,16 @@
         </is>
       </c>
       <c r="G184">
-        <v>36666.74999999999</v>
+        <v>259000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="D185">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -6092,16 +6092,16 @@
         </is>
       </c>
       <c r="G185">
-        <v>1</v>
+        <v>3114583333.333333</v>
       </c>
     </row>
     <row r="186">
       <c r="A186">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6110,7 +6110,7 @@
         </is>
       </c>
       <c r="D186">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -6123,16 +6123,16 @@
         </is>
       </c>
       <c r="G186">
-        <v>5800000</v>
+        <v>172750000</v>
       </c>
     </row>
     <row r="187">
       <c r="A187">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6141,7 +6141,7 @@
         </is>
       </c>
       <c r="D187">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -6154,16 +6154,16 @@
         </is>
       </c>
       <c r="G187">
-        <v>483333.4166666667</v>
+        <v>273944444.4444444</v>
       </c>
     </row>
     <row r="188">
       <c r="A188">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="D188">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6185,16 +6185,16 @@
         </is>
       </c>
       <c r="G188">
-        <v>1</v>
+        <v>3212500000</v>
       </c>
     </row>
     <row r="189">
       <c r="A189">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="D189">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6216,16 +6216,16 @@
         </is>
       </c>
       <c r="G189">
-        <v>12450000</v>
+        <v>465000000</v>
       </c>
     </row>
     <row r="190">
       <c r="A190">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6234,7 +6234,7 @@
         </is>
       </c>
       <c r="D190">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6247,16 +6247,16 @@
         </is>
       </c>
       <c r="G190">
-        <v>1037500.083333333</v>
+        <v>306458333.3333333</v>
       </c>
     </row>
     <row r="191">
       <c r="A191">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="D191">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6278,16 +6278,16 @@
         </is>
       </c>
       <c r="G191">
-        <v>1</v>
+        <v>51250000</v>
       </c>
     </row>
     <row r="192">
       <c r="A192">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6296,7 +6296,7 @@
         </is>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6309,16 +6309,16 @@
         </is>
       </c>
       <c r="G192">
-        <v>51000000</v>
+        <v>2616000000</v>
       </c>
     </row>
     <row r="193">
       <c r="A193">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="D193">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6340,16 +6340,16 @@
         </is>
       </c>
       <c r="G193">
-        <v>4250000.083333333</v>
+        <v>222270833.3333333</v>
       </c>
     </row>
     <row r="194">
       <c r="A194">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="D194">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -6371,16 +6371,16 @@
         </is>
       </c>
       <c r="G194">
-        <v>1</v>
+        <v>6625000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6389,7 +6389,7 @@
         </is>
       </c>
       <c r="D195">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -6402,16 +6402,16 @@
         </is>
       </c>
       <c r="G195">
-        <v>56000000</v>
+        <v>1095000000</v>
       </c>
     </row>
     <row r="196">
       <c r="A196">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="D196">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6433,16 +6433,16 @@
         </is>
       </c>
       <c r="G196">
-        <v>4666666.75</v>
+        <v>643333333.3333334</v>
       </c>
     </row>
     <row r="197">
       <c r="A197">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6451,7 +6451,7 @@
         </is>
       </c>
       <c r="D197">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6464,16 +6464,16 @@
         </is>
       </c>
       <c r="G197">
-        <v>16250</v>
+        <v>9500000000</v>
       </c>
     </row>
     <row r="198">
       <c r="A198">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6482,7 +6482,7 @@
         </is>
       </c>
       <c r="D198">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6495,16 +6495,16 @@
         </is>
       </c>
       <c r="G198">
-        <v>87000000</v>
+        <v>1410000000</v>
       </c>
     </row>
     <row r="199">
       <c r="A199">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6513,7 +6513,7 @@
         </is>
       </c>
       <c r="D199">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6526,16 +6526,16 @@
         </is>
       </c>
       <c r="G199">
-        <v>7251354.166666667</v>
+        <v>909166666.6666666</v>
       </c>
     </row>
     <row r="200">
       <c r="A200">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6544,7 +6544,7 @@
         </is>
       </c>
       <c r="D200">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6557,16 +6557,16 @@
         </is>
       </c>
       <c r="G200">
-        <v>25750</v>
+        <v>43750000</v>
       </c>
     </row>
     <row r="201">
       <c r="A201">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="D201">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6588,16 +6588,16 @@
         </is>
       </c>
       <c r="G201">
-        <v>231000000</v>
+        <v>195000000</v>
       </c>
     </row>
     <row r="202">
       <c r="A202">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6606,7 +6606,7 @@
         </is>
       </c>
       <c r="D202">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6619,16 +6619,16 @@
         </is>
       </c>
       <c r="G202">
-        <v>19252145.83333333</v>
+        <v>19895833.33333333</v>
       </c>
     </row>
     <row r="203">
       <c r="A203">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="D203">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6650,16 +6650,16 @@
         </is>
       </c>
       <c r="G203">
-        <v>35375</v>
+        <v>332500000</v>
       </c>
     </row>
     <row r="204">
       <c r="A204">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6668,7 +6668,7 @@
         </is>
       </c>
       <c r="D204">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6681,16 +6681,16 @@
         </is>
       </c>
       <c r="G204">
-        <v>160500000</v>
+        <v>52500000</v>
       </c>
     </row>
     <row r="205">
       <c r="A205">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="D205">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6712,16 +6712,16 @@
         </is>
       </c>
       <c r="G205">
-        <v>13377947.91666667</v>
+        <v>32083333.33333333</v>
       </c>
     </row>
     <row r="206">
       <c r="A206">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="D206">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -6743,16 +6743,16 @@
         </is>
       </c>
       <c r="G206">
-        <v>22000</v>
+        <v>81250000</v>
       </c>
     </row>
     <row r="207">
       <c r="A207">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="D207">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -6774,16 +6774,16 @@
         </is>
       </c>
       <c r="G207">
-        <v>181500000</v>
+        <v>37500000</v>
       </c>
     </row>
     <row r="208">
       <c r="A208">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="D208">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -6805,16 +6805,16 @@
         </is>
       </c>
       <c r="G208">
-        <v>15126833.33333333</v>
+        <v>9895833.333333334</v>
       </c>
     </row>
     <row r="209">
       <c r="A209">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6836,16 +6836,16 @@
         </is>
       </c>
       <c r="G209">
-        <v>2912500000</v>
+        <v>3012500000</v>
       </c>
     </row>
     <row r="210">
       <c r="A210">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6867,16 +6867,16 @@
         </is>
       </c>
       <c r="G210">
-        <v>195500000</v>
+        <v>521250000</v>
       </c>
     </row>
     <row r="211">
       <c r="A211">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6898,16 +6898,16 @@
         </is>
       </c>
       <c r="G211">
-        <v>259000000</v>
+        <v>294479166.6666667</v>
       </c>
     </row>
     <row r="212">
       <c r="A212">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -6929,16 +6929,16 @@
         </is>
       </c>
       <c r="G212">
-        <v>3114583333.333333</v>
+        <v>3016666666.666666</v>
       </c>
     </row>
     <row r="213">
       <c r="A213">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6960,16 +6960,16 @@
         </is>
       </c>
       <c r="G213">
-        <v>172750000</v>
+        <v>304500000</v>
       </c>
     </row>
     <row r="214">
       <c r="A214">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6991,16 +6991,16 @@
         </is>
       </c>
       <c r="G214">
-        <v>273944444.4444444</v>
+        <v>276763888.8888888</v>
       </c>
     </row>
     <row r="215">
       <c r="A215">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7022,16 +7022,16 @@
         </is>
       </c>
       <c r="G215">
-        <v>3212500000</v>
+        <v>2012500000</v>
       </c>
     </row>
     <row r="216">
       <c r="A216">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7053,16 +7053,16 @@
         </is>
       </c>
       <c r="G216">
-        <v>465000000</v>
+        <v>510000000</v>
       </c>
     </row>
     <row r="217">
       <c r="A217">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -7084,16 +7084,16 @@
         </is>
       </c>
       <c r="G217">
-        <v>306458333.3333333</v>
+        <v>210208333.3333333</v>
       </c>
     </row>
     <row r="218">
       <c r="A218">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="D218">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -7115,16 +7115,16 @@
         </is>
       </c>
       <c r="G218">
-        <v>1</v>
+        <v>3875000000</v>
       </c>
     </row>
     <row r="219">
       <c r="A219">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -7133,7 +7133,7 @@
         </is>
       </c>
       <c r="D219">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -7146,16 +7146,16 @@
         </is>
       </c>
       <c r="G219">
-        <v>8250000</v>
+        <v>319500000</v>
       </c>
     </row>
     <row r="220">
       <c r="A220">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -7164,7 +7164,7 @@
         </is>
       </c>
       <c r="D220">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -7177,16 +7177,16 @@
         </is>
       </c>
       <c r="G220">
-        <v>687500.0833333334</v>
+        <v>349541666.6666667</v>
       </c>
     </row>
     <row r="221">
       <c r="A221">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="D221">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -7208,16 +7208,16 @@
         </is>
       </c>
       <c r="G221">
-        <v>1</v>
+        <v>3283333333.333334</v>
       </c>
     </row>
     <row r="222">
       <c r="A222">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="D222">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -7239,16 +7239,16 @@
         </is>
       </c>
       <c r="G222">
-        <v>43200000</v>
+        <v>423000000</v>
       </c>
     </row>
     <row r="223">
       <c r="A223">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -7257,7 +7257,7 @@
         </is>
       </c>
       <c r="D223">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -7270,16 +7270,16 @@
         </is>
       </c>
       <c r="G223">
-        <v>3600000.083333333</v>
+        <v>308861111.1111112</v>
       </c>
     </row>
     <row r="224">
       <c r="A224">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="D224">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -7301,16 +7301,16 @@
         </is>
       </c>
       <c r="G224">
-        <v>1</v>
+        <v>4075000000</v>
       </c>
     </row>
     <row r="225">
       <c r="A225">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7319,7 +7319,7 @@
         </is>
       </c>
       <c r="D225">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -7332,16 +7332,16 @@
         </is>
       </c>
       <c r="G225">
-        <v>17400000</v>
+        <v>259500000</v>
       </c>
     </row>
     <row r="226">
       <c r="A226">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>h.taenio</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="D226">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -7363,16 +7363,16 @@
         </is>
       </c>
       <c r="G226">
-        <v>1450000.083333333</v>
+        <v>361208333.3333333</v>
       </c>
     </row>
     <row r="227">
       <c r="A227">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="D227">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -7394,16 +7394,16 @@
         </is>
       </c>
       <c r="G227">
-        <v>51250000</v>
+        <v>3933333333.333334</v>
       </c>
     </row>
     <row r="228">
       <c r="A228">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7412,7 +7412,7 @@
         </is>
       </c>
       <c r="D228">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -7425,16 +7425,16 @@
         </is>
       </c>
       <c r="G228">
-        <v>2616000000</v>
+        <v>434250000</v>
       </c>
     </row>
     <row r="229">
       <c r="A229">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7443,7 +7443,7 @@
         </is>
       </c>
       <c r="D229">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -7456,16 +7456,16 @@
         </is>
       </c>
       <c r="G229">
-        <v>222270833.3333333</v>
+        <v>363965277.7777779</v>
       </c>
     </row>
     <row r="230">
       <c r="A230">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7474,7 +7474,7 @@
         </is>
       </c>
       <c r="D230">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -7487,16 +7487,16 @@
         </is>
       </c>
       <c r="G230">
-        <v>6625000000</v>
+        <v>2250000000</v>
       </c>
     </row>
     <row r="231">
       <c r="A231">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -7505,7 +7505,7 @@
         </is>
       </c>
       <c r="D231">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -7518,16 +7518,16 @@
         </is>
       </c>
       <c r="G231">
-        <v>1095000000</v>
+        <v>280500000</v>
       </c>
     </row>
     <row r="232">
       <c r="A232">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7536,7 +7536,7 @@
         </is>
       </c>
       <c r="D232">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -7549,16 +7549,16 @@
         </is>
       </c>
       <c r="G232">
-        <v>643333333.3333334</v>
+        <v>210875000</v>
       </c>
     </row>
     <row r="233">
       <c r="A233">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="D233">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -7580,16 +7580,16 @@
         </is>
       </c>
       <c r="G233">
-        <v>9500000000</v>
+        <v>1608125000</v>
       </c>
     </row>
     <row r="234">
       <c r="A234">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -7598,7 +7598,7 @@
         </is>
       </c>
       <c r="D234">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -7611,16 +7611,16 @@
         </is>
       </c>
       <c r="G234">
-        <v>1410000000</v>
+        <v>15000000</v>
       </c>
     </row>
     <row r="235">
       <c r="A235">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>n.aroma</t>
+          <t>p.putida</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="D235">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -7642,16 +7642,16 @@
         </is>
       </c>
       <c r="G235">
-        <v>909166666.6666666</v>
+        <v>135260416.6666667</v>
       </c>
     </row>
     <row r="236">
       <c r="A236">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7660,7 +7660,7 @@
         </is>
       </c>
       <c r="D236">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -7673,16 +7673,16 @@
         </is>
       </c>
       <c r="G236">
-        <v>43750000</v>
+        <v>3441666666.666666</v>
       </c>
     </row>
     <row r="237">
       <c r="A237">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="D237">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -7704,16 +7704,16 @@
         </is>
       </c>
       <c r="G237">
-        <v>195000000</v>
+        <v>675000000</v>
       </c>
     </row>
     <row r="238">
       <c r="A238">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -7722,7 +7722,7 @@
         </is>
       </c>
       <c r="D238">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -7735,16 +7735,16 @@
         </is>
       </c>
       <c r="G238">
-        <v>19895833.33333333</v>
+        <v>343055555.5555555</v>
       </c>
     </row>
     <row r="239">
       <c r="A239">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="D239">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -7766,16 +7766,16 @@
         </is>
       </c>
       <c r="G239">
-        <v>332500000</v>
+        <v>2233333333.333333</v>
       </c>
     </row>
     <row r="240">
       <c r="A240">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -7784,7 +7784,7 @@
         </is>
       </c>
       <c r="D240">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -7797,16 +7797,16 @@
         </is>
       </c>
       <c r="G240">
-        <v>52500000</v>
+        <v>3495000000</v>
       </c>
     </row>
     <row r="241">
       <c r="A241">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -7815,7 +7815,7 @@
         </is>
       </c>
       <c r="D241">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -7828,16 +7828,16 @@
         </is>
       </c>
       <c r="G241">
-        <v>32083333.33333333</v>
+        <v>477361111.1111112</v>
       </c>
     </row>
     <row r="242">
       <c r="A242">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="D242">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -7859,16 +7859,16 @@
         </is>
       </c>
       <c r="G242">
-        <v>81250000</v>
+        <v>2725000000</v>
       </c>
     </row>
     <row r="243">
       <c r="A243">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="D243">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -7890,16 +7890,16 @@
         </is>
       </c>
       <c r="G243">
-        <v>37500000</v>
+        <v>7800000000</v>
       </c>
     </row>
     <row r="244">
       <c r="A244">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>n.penta</t>
+          <t>n.aroma</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7908,7 +7908,7 @@
         </is>
       </c>
       <c r="D244">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -7921,16 +7921,16 @@
         </is>
       </c>
       <c r="G244">
-        <v>9895833.333333334</v>
+        <v>877083333.3333334</v>
       </c>
     </row>
     <row r="245">
       <c r="A245">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -7939,7 +7939,7 @@
         </is>
       </c>
       <c r="D245">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -7952,16 +7952,16 @@
         </is>
       </c>
       <c r="G245">
-        <v>3012500000</v>
+        <v>78125000</v>
       </c>
     </row>
     <row r="246">
       <c r="A246">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="D246">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -7983,16 +7983,16 @@
         </is>
       </c>
       <c r="G246">
-        <v>521250000</v>
+        <v>45000000</v>
       </c>
     </row>
     <row r="247">
       <c r="A247">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -8001,7 +8001,7 @@
         </is>
       </c>
       <c r="D247">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -8014,16 +8014,16 @@
         </is>
       </c>
       <c r="G247">
-        <v>294479166.6666667</v>
+        <v>10260416.66666667</v>
       </c>
     </row>
     <row r="248">
       <c r="A248">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="D248">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -8045,16 +8045,16 @@
         </is>
       </c>
       <c r="G248">
-        <v>3016666666.666666</v>
+        <v>93750000</v>
       </c>
     </row>
     <row r="249">
       <c r="A249">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -8063,7 +8063,7 @@
         </is>
       </c>
       <c r="D249">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -8076,16 +8076,16 @@
         </is>
       </c>
       <c r="G249">
-        <v>304500000</v>
+        <v>31500000</v>
       </c>
     </row>
     <row r="250">
       <c r="A250">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="D250">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -8107,16 +8107,16 @@
         </is>
       </c>
       <c r="G250">
-        <v>276763888.8888888</v>
+        <v>10437500</v>
       </c>
     </row>
     <row r="251">
       <c r="A251">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="D251">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -8138,16 +8138,16 @@
         </is>
       </c>
       <c r="G251">
-        <v>2012500000</v>
+        <v>431250000</v>
       </c>
     </row>
     <row r="252">
       <c r="A252">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -8156,7 +8156,7 @@
         </is>
       </c>
       <c r="D252">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -8169,16 +8169,16 @@
         </is>
       </c>
       <c r="G252">
-        <v>510000000</v>
+        <v>109500000</v>
       </c>
     </row>
     <row r="253">
       <c r="A253">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>m.fred</t>
+          <t>n.penta</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="D253">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -8200,16 +8200,16 @@
         </is>
       </c>
       <c r="G253">
-        <v>210208333.3333333</v>
+        <v>45062500</v>
       </c>
     </row>
     <row r="254">
       <c r="A254">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -8218,7 +8218,7 @@
         </is>
       </c>
       <c r="D254">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -8231,16 +8231,16 @@
         </is>
       </c>
       <c r="G254">
-        <v>3875000000</v>
+        <v>1187500000</v>
       </c>
     </row>
     <row r="255">
       <c r="A255">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -8249,7 +8249,7 @@
         </is>
       </c>
       <c r="D255">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -8262,16 +8262,16 @@
         </is>
       </c>
       <c r="G255">
-        <v>319500000</v>
+        <v>142500000</v>
       </c>
     </row>
     <row r="256">
       <c r="A256">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -8280,7 +8280,7 @@
         </is>
       </c>
       <c r="D256">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -8293,16 +8293,16 @@
         </is>
       </c>
       <c r="G256">
-        <v>349541666.6666667</v>
+        <v>110833333.3333333</v>
       </c>
     </row>
     <row r="257">
       <c r="A257">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -8311,7 +8311,7 @@
         </is>
       </c>
       <c r="D257">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -8324,16 +8324,16 @@
         </is>
       </c>
       <c r="G257">
-        <v>3283333333.333334</v>
+        <v>1837500000</v>
       </c>
     </row>
     <row r="258">
       <c r="A258">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -8342,7 +8342,7 @@
         </is>
       </c>
       <c r="D258">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -8355,16 +8355,16 @@
         </is>
       </c>
       <c r="G258">
-        <v>423000000</v>
+        <v>102000000</v>
       </c>
     </row>
     <row r="259">
       <c r="A259">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -8373,7 +8373,7 @@
         </is>
       </c>
       <c r="D259">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -8386,16 +8386,16 @@
         </is>
       </c>
       <c r="G259">
-        <v>308861111.1111112</v>
+        <v>161625000</v>
       </c>
     </row>
     <row r="260">
       <c r="A260">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -8404,7 +8404,7 @@
         </is>
       </c>
       <c r="D260">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -8417,16 +8417,16 @@
         </is>
       </c>
       <c r="G260">
-        <v>4075000000</v>
+        <v>550000000</v>
       </c>
     </row>
     <row r="261">
       <c r="A261">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -8435,7 +8435,7 @@
         </is>
       </c>
       <c r="D261">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -8448,16 +8448,16 @@
         </is>
       </c>
       <c r="G261">
-        <v>259500000</v>
+        <v>84000000</v>
       </c>
     </row>
     <row r="262">
       <c r="A262">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>a.venet</t>
+          <t>m.fred</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -8466,7 +8466,7 @@
         </is>
       </c>
       <c r="D262">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -8479,16 +8479,16 @@
         </is>
       </c>
       <c r="G262">
-        <v>361208333.3333333</v>
+        <v>52833333.33333334</v>
       </c>
     </row>
     <row r="263">
       <c r="A263">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -8510,16 +8510,16 @@
         </is>
       </c>
       <c r="G263">
-        <v>3933333333.333334</v>
+        <v>862500000</v>
       </c>
     </row>
     <row r="264">
       <c r="A264">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8541,16 +8541,16 @@
         </is>
       </c>
       <c r="G264">
-        <v>434250000</v>
+        <v>79500000</v>
       </c>
     </row>
     <row r="265">
       <c r="A265">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -8572,16 +8572,16 @@
         </is>
       </c>
       <c r="G265">
-        <v>363965277.7777779</v>
+        <v>78500000</v>
       </c>
     </row>
     <row r="266">
       <c r="A266">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -8603,16 +8603,16 @@
         </is>
       </c>
       <c r="G266">
-        <v>2250000000</v>
+        <v>1537500000</v>
       </c>
     </row>
     <row r="267">
       <c r="A267">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -8634,16 +8634,16 @@
         </is>
       </c>
       <c r="G267">
-        <v>280500000</v>
+        <v>885000000</v>
       </c>
     </row>
     <row r="268">
       <c r="A268">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -8665,16 +8665,16 @@
         </is>
       </c>
       <c r="G268">
-        <v>210875000</v>
+        <v>201875000</v>
       </c>
     </row>
     <row r="269">
       <c r="A269">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -8696,16 +8696,16 @@
         </is>
       </c>
       <c r="G269">
-        <v>1608125000</v>
+        <v>2312500000</v>
       </c>
     </row>
     <row r="270">
       <c r="A270">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -8727,16 +8727,16 @@
         </is>
       </c>
       <c r="G270">
-        <v>15000000</v>
+        <v>166500000</v>
       </c>
     </row>
     <row r="271">
       <c r="A271">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>p.putida</t>
+          <t>a.venet</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -8758,1681 +8758,7 @@
         </is>
       </c>
       <c r="G271">
-        <v>135260416.6666667</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272">
-        <v>3</v>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>n.aroma</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D272">
-        <v>42</v>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>super_total</t>
-        </is>
-      </c>
-      <c r="G272">
-        <v>3441666666.666666</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273">
-        <v>3</v>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>n.aroma</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D273">
-        <v>42</v>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>capsule_total</t>
-        </is>
-      </c>
-      <c r="G273">
-        <v>675000000</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274">
-        <v>3</v>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>n.aroma</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D274">
-        <v>42</v>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>total_conc</t>
-        </is>
-      </c>
-      <c r="G274">
-        <v>343055555.5555555</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275">
-        <v>3</v>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>n.aroma</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D275">
-        <v>42</v>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>super_total</t>
-        </is>
-      </c>
-      <c r="G275">
-        <v>2233333333.333333</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276">
-        <v>3</v>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>n.aroma</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D276">
-        <v>42</v>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>capsule_total</t>
-        </is>
-      </c>
-      <c r="G276">
-        <v>3495000000</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277">
-        <v>3</v>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>n.aroma</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D277">
-        <v>42</v>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>total_conc</t>
-        </is>
-      </c>
-      <c r="G277">
-        <v>477361111.1111112</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278">
-        <v>3</v>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>n.aroma</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D278">
-        <v>42</v>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>super_total</t>
-        </is>
-      </c>
-      <c r="G278">
-        <v>2725000000</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279">
-        <v>3</v>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>n.aroma</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D279">
-        <v>42</v>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>capsule_total</t>
-        </is>
-      </c>
-      <c r="G279">
-        <v>7800000000</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280">
-        <v>3</v>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>n.aroma</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D280">
-        <v>42</v>
-      </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>total_conc</t>
-        </is>
-      </c>
-      <c r="G280">
-        <v>877083333.3333334</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281">
-        <v>7</v>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>h.taenio</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D281">
-        <v>21</v>
-      </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>super_total</t>
-        </is>
-      </c>
-      <c r="G281">
-        <v>3383333333.333333</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282">
-        <v>7</v>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>h.taenio</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D282">
-        <v>21</v>
-      </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>capsule_total</t>
-        </is>
-      </c>
-      <c r="G282">
-        <v>450000000</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283">
-        <v>7</v>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>h.taenio</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D283">
-        <v>21</v>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>total_conc</t>
-        </is>
-      </c>
-      <c r="G283">
-        <v>319444444.4444444</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284">
-        <v>7</v>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>h.taenio</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D284">
-        <v>21</v>
-      </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>super_total</t>
-        </is>
-      </c>
-      <c r="G284">
-        <v>1475000000</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285">
-        <v>7</v>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>h.taenio</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D285">
-        <v>21</v>
-      </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>capsule_total</t>
-        </is>
-      </c>
-      <c r="G285">
-        <v>67500000</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286">
-        <v>7</v>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>h.taenio</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D286">
-        <v>21</v>
-      </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>total_conc</t>
-        </is>
-      </c>
-      <c r="G286">
-        <v>128541666.6666667</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287">
-        <v>7</v>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>h.taenio</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D287">
-        <v>21</v>
-      </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>super_total</t>
-        </is>
-      </c>
-      <c r="G287">
-        <v>1937500000</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288">
-        <v>7</v>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>h.taenio</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D288">
-        <v>21</v>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>capsule_total</t>
-        </is>
-      </c>
-      <c r="G288">
-        <v>168000000</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289">
-        <v>7</v>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>h.taenio</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D289">
-        <v>21</v>
-      </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>total_conc</t>
-        </is>
-      </c>
-      <c r="G289">
-        <v>175458333.3333333</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290">
-        <v>4</v>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>n.penta</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D290">
-        <v>42</v>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>super_total</t>
-        </is>
-      </c>
-      <c r="G290">
-        <v>78125000</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291">
-        <v>4</v>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>n.penta</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D291">
-        <v>42</v>
-      </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>capsule_total</t>
-        </is>
-      </c>
-      <c r="G291">
-        <v>45000000</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292">
-        <v>4</v>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>n.penta</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D292">
-        <v>42</v>
-      </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>total_conc</t>
-        </is>
-      </c>
-      <c r="G292">
-        <v>10260416.66666667</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293">
-        <v>4</v>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>n.penta</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D293">
-        <v>42</v>
-      </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>super_total</t>
-        </is>
-      </c>
-      <c r="G293">
-        <v>93750000</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294">
-        <v>4</v>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>n.penta</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D294">
-        <v>42</v>
-      </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>capsule_total</t>
-        </is>
-      </c>
-      <c r="G294">
-        <v>31500000</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295">
-        <v>4</v>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>n.penta</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D295">
-        <v>42</v>
-      </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>total_conc</t>
-        </is>
-      </c>
-      <c r="G295">
-        <v>10437500</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296">
-        <v>4</v>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>n.penta</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D296">
-        <v>42</v>
-      </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>super_total</t>
-        </is>
-      </c>
-      <c r="G296">
-        <v>431250000</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297">
-        <v>4</v>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>n.penta</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D297">
-        <v>42</v>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>capsule_total</t>
-        </is>
-      </c>
-      <c r="G297">
-        <v>109500000</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298">
-        <v>4</v>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>n.penta</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D298">
-        <v>42</v>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>total_conc</t>
-        </is>
-      </c>
-      <c r="G298">
-        <v>45062500</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299">
-        <v>5</v>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>m.fred</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D299">
-        <v>42</v>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>super_total</t>
-        </is>
-      </c>
-      <c r="G299">
-        <v>1187500000</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300">
-        <v>5</v>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>m.fred</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D300">
-        <v>42</v>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>capsule_total</t>
-        </is>
-      </c>
-      <c r="G300">
-        <v>142500000</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301">
-        <v>5</v>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>m.fred</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D301">
-        <v>42</v>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>total_conc</t>
-        </is>
-      </c>
-      <c r="G301">
-        <v>110833333.3333333</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302">
-        <v>5</v>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>m.fred</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D302">
-        <v>42</v>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>super_total</t>
-        </is>
-      </c>
-      <c r="G302">
-        <v>1837500000</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303">
-        <v>5</v>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>m.fred</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D303">
-        <v>42</v>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>capsule_total</t>
-        </is>
-      </c>
-      <c r="G303">
-        <v>102000000</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304">
-        <v>5</v>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>m.fred</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D304">
-        <v>42</v>
-      </c>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>total_conc</t>
-        </is>
-      </c>
-      <c r="G304">
-        <v>161625000</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305">
-        <v>5</v>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>m.fred</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D305">
-        <v>42</v>
-      </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>super_total</t>
-        </is>
-      </c>
-      <c r="G305">
-        <v>550000000</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306">
-        <v>5</v>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>m.fred</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D306">
-        <v>42</v>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>capsule_total</t>
-        </is>
-      </c>
-      <c r="G306">
-        <v>84000000</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307">
-        <v>5</v>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>m.fred</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D307">
-        <v>42</v>
-      </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>total_conc</t>
-        </is>
-      </c>
-      <c r="G307">
-        <v>52833333.33333334</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308">
-        <v>6</v>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>a.venet</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D308">
-        <v>42</v>
-      </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>super_total</t>
-        </is>
-      </c>
-      <c r="G308">
-        <v>862500000</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309">
-        <v>6</v>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>a.venet</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D309">
-        <v>42</v>
-      </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t>capsule_total</t>
-        </is>
-      </c>
-      <c r="G309">
-        <v>79500000</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310">
-        <v>6</v>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>a.venet</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D310">
-        <v>42</v>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>total_conc</t>
-        </is>
-      </c>
-      <c r="G310">
-        <v>78500000</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311">
-        <v>6</v>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>a.venet</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D311">
-        <v>42</v>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t>super_total</t>
-        </is>
-      </c>
-      <c r="G311">
-        <v>1537500000</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312">
-        <v>6</v>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>a.venet</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D312">
-        <v>42</v>
-      </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>capsule_total</t>
-        </is>
-      </c>
-      <c r="G312">
-        <v>885000000</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313">
-        <v>6</v>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>a.venet</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D313">
-        <v>42</v>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F313" t="inlineStr">
-        <is>
-          <t>total_conc</t>
-        </is>
-      </c>
-      <c r="G313">
-        <v>201875000</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314">
-        <v>6</v>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>a.venet</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D314">
-        <v>42</v>
-      </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t>super_total</t>
-        </is>
-      </c>
-      <c r="G314">
-        <v>2312500000</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315">
-        <v>6</v>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>a.venet</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D315">
-        <v>42</v>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>capsule_total</t>
-        </is>
-      </c>
-      <c r="G315">
-        <v>166500000</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316">
-        <v>6</v>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>a.venet</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D316">
-        <v>42</v>
-      </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>total_conc</t>
-        </is>
-      </c>
-      <c r="G316">
         <v>206583333.3333333</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317">
-        <v>7</v>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>h.taenio</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D317">
-        <v>42</v>
-      </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>super_total</t>
-        </is>
-      </c>
-      <c r="G317">
-        <v>268333333.3333333</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318">
-        <v>7</v>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>h.taenio</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D318">
-        <v>42</v>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>capsule_total</t>
-        </is>
-      </c>
-      <c r="G318">
-        <v>13200000</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319">
-        <v>7</v>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>h.taenio</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D319">
-        <v>42</v>
-      </c>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>total_conc</t>
-        </is>
-      </c>
-      <c r="G319">
-        <v>23461111.11111111</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320">
-        <v>7</v>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>h.taenio</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D320">
-        <v>42</v>
-      </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>super_total</t>
-        </is>
-      </c>
-      <c r="G320">
-        <v>1087500000</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321">
-        <v>7</v>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>h.taenio</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D321">
-        <v>42</v>
-      </c>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>capsule_total</t>
-        </is>
-      </c>
-      <c r="G321">
-        <v>88500000</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322">
-        <v>7</v>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>h.taenio</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D322">
-        <v>42</v>
-      </c>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>total_conc</t>
-        </is>
-      </c>
-      <c r="G322">
-        <v>98000000</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323">
-        <v>7</v>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>h.taenio</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D323">
-        <v>42</v>
-      </c>
-      <c r="E323" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>super_total</t>
-        </is>
-      </c>
-      <c r="G323">
-        <v>1287500000</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324">
-        <v>7</v>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>h.taenio</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D324">
-        <v>42</v>
-      </c>
-      <c r="E324" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>capsule_total</t>
-        </is>
-      </c>
-      <c r="G324">
-        <v>123000000</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325">
-        <v>7</v>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>h.taenio</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D325">
-        <v>42</v>
-      </c>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>encapsulated</t>
-        </is>
-      </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>total_conc</t>
-        </is>
-      </c>
-      <c r="G325">
-        <v>117541666.6666667</v>
       </c>
     </row>
   </sheetData>
